--- a/docs/design-vi/ACSMS-SCR-026/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者名簿出力画面_v1.0.xlsx
+++ b/docs/design-vi/ACSMS-SCR-026/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者名簿出力画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1363,20 +1363,78 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="inlineStr"/>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>Đồng bộ với bản tiếng Nhật: tạo カテゴリ6 và bổ sung 3 ca (042〜044). 042＝lọc theo chi nhánh (điều kiện tùy chọn, người đọc có shiten_id NULL — vốn luôn NULL với người nhập từ liên kết bản điện tử — bị loại khi chọn chi nhánh). 043＝tách đối tượng tổng hợp theo loại báo biểu (#56597): theo cửa hàng bán ＝ chỉ bản giấy; theo chi nhánh quản lý ＝ bản giấy (vô điều kiện) ＋ kết hợp (trả phí) ＋ bản điện tử (trả phí và đã duyệt). 044＝loại cửa hàng bán dummy khỏi lựa chọn (`dummy=exclude`)</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6239,7 +6297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ57"/>
+  <dimension ref="A1:BQ61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -13850,9 +13908,367 @@
       <c r="BP57" s="10" t="n"/>
       <c r="BQ57" s="11" t="n"/>
     </row>
+    <row r="58" ht="22.5" customHeight="1">
+      <c r="A58" s="32" t="inlineStr">
+        <is>
+          <t>カテゴリ6: Đối tượng tổng hợp・Lựa chọn cửa hàng bán (Scope / Hanbaiten Options)</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="10" t="n"/>
+      <c r="J58" s="10" t="n"/>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="10" t="n"/>
+      <c r="Q58" s="10" t="n"/>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="10" t="n"/>
+      <c r="X58" s="10" t="n"/>
+      <c r="Y58" s="10" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="10" t="n"/>
+      <c r="AE58" s="10" t="n"/>
+      <c r="AF58" s="10" t="n"/>
+      <c r="AG58" s="10" t="n"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="10" t="n"/>
+      <c r="AJ58" s="10" t="n"/>
+      <c r="AK58" s="10" t="n"/>
+      <c r="AL58" s="10" t="n"/>
+      <c r="AM58" s="10" t="n"/>
+      <c r="AN58" s="10" t="n"/>
+      <c r="AO58" s="10" t="n"/>
+      <c r="AP58" s="10" t="n"/>
+      <c r="AQ58" s="10" t="n"/>
+      <c r="AR58" s="10" t="n"/>
+      <c r="AS58" s="10" t="n"/>
+      <c r="AT58" s="10" t="n"/>
+      <c r="AU58" s="10" t="n"/>
+      <c r="AV58" s="10" t="n"/>
+      <c r="AW58" s="10" t="n"/>
+      <c r="AX58" s="10" t="n"/>
+      <c r="AY58" s="10" t="n"/>
+      <c r="AZ58" s="10" t="n"/>
+      <c r="BA58" s="10" t="n"/>
+      <c r="BB58" s="10" t="n"/>
+      <c r="BC58" s="10" t="n"/>
+      <c r="BD58" s="10" t="n"/>
+      <c r="BE58" s="10" t="n"/>
+      <c r="BF58" s="10" t="n"/>
+      <c r="BG58" s="10" t="n"/>
+      <c r="BH58" s="10" t="n"/>
+      <c r="BI58" s="10" t="n"/>
+      <c r="BJ58" s="10" t="n"/>
+      <c r="BK58" s="10" t="n"/>
+      <c r="BL58" s="10" t="n"/>
+      <c r="BM58" s="10" t="n"/>
+      <c r="BN58" s="10" t="n"/>
+      <c r="BO58" s="10" t="n"/>
+      <c r="BP58" s="10" t="n"/>
+      <c r="BQ58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="272" customHeight="1">
+      <c r="A59" s="44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B59" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-026-042</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="46" t="inlineStr">
+        <is>
+          <t>Lọc theo chi nhánh (chỉ với loại báo biểu theo chi nhánh quản lý・điều kiện tùy chọn)</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="11" t="n"/>
+      <c r="J59" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (ja_id=100・có quyền `report.export_meibo`)
+・Dưới chi nhánh quản lý A (kanri_shiten_id=10) có chi nhánh X (shiten_id=21)／chi nhánh Y (shiten_id=22)
+・Dưới chi nhánh quản lý B (kanri_shiten_id=11) có chi nhánh Z (shiten_id=31)
+・Người đọc còn hiệu lực tại thời điểm ngày áp dụng: chi nhánh X có 3 người, chi nhánh Y có 2 người, chưa đặt chi nhánh (shiten_id là NULL) có 1 người (tất cả đều thuộc chi nhánh quản lý A)</t>
+        </is>
+      </c>
+      <c r="K59" s="10" t="n"/>
+      <c r="L59" s="10" t="n"/>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="11" t="n"/>
+      <c r="Q59" s="46" t="inlineStr"/>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="10" t="n"/>
+      <c r="T59" s="10" t="n"/>
+      <c r="U59" s="10" t="n"/>
+      <c r="V59" s="10" t="n"/>
+      <c r="W59" s="11" t="n"/>
+      <c r="X59" s="46" t="inlineStr"/>
+      <c r="Y59" s="10" t="n"/>
+      <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="10" t="n"/>
+      <c r="AB59" s="10" t="n"/>
+      <c r="AC59" s="10" t="n"/>
+      <c r="AD59" s="11" t="n"/>
+      <c r="AE59" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF59" s="11" t="n"/>
+      <c r="AG59" s="45" t="inlineStr"/>
+      <c r="AH59" s="10" t="n"/>
+      <c r="AI59" s="11" t="n"/>
+      <c r="AJ59" s="45" t="inlineStr"/>
+      <c r="AK59" s="10" t="n"/>
+      <c r="AL59" s="11" t="n"/>
+      <c r="AM59" s="45" t="inlineStr"/>
+      <c r="AN59" s="10" t="n"/>
+      <c r="AO59" s="11" t="n"/>
+      <c r="AP59" s="45" t="inlineStr"/>
+      <c r="AQ59" s="10" t="n"/>
+      <c r="AR59" s="11" t="n"/>
+      <c r="AS59" s="45" t="inlineStr"/>
+      <c r="AT59" s="10" t="n"/>
+      <c r="AU59" s="11" t="n"/>
+      <c r="AV59" s="45" t="inlineStr"/>
+      <c r="AW59" s="10" t="n"/>
+      <c r="AX59" s="11" t="n"/>
+      <c r="AY59" s="45" t="inlineStr"/>
+      <c r="AZ59" s="10" t="n"/>
+      <c r="BA59" s="11" t="n"/>
+      <c r="BB59" s="45" t="inlineStr"/>
+      <c r="BC59" s="10" t="n"/>
+      <c r="BD59" s="11" t="n"/>
+      <c r="BE59" s="45" t="inlineStr"/>
+      <c r="BF59" s="10" t="n"/>
+      <c r="BG59" s="11" t="n"/>
+      <c r="BH59" s="45" t="inlineStr"/>
+      <c r="BI59" s="10" t="n"/>
+      <c r="BJ59" s="11" t="n"/>
+      <c r="BK59" s="46" t="inlineStr"/>
+      <c r="BL59" s="10" t="n"/>
+      <c r="BM59" s="10" t="n"/>
+      <c r="BN59" s="10" t="n"/>
+      <c r="BO59" s="10" t="n"/>
+      <c r="BP59" s="10" t="n"/>
+      <c r="BQ59" s="11" t="n"/>
+    </row>
+    <row r="60" ht="368" customHeight="1">
+      <c r="A60" s="44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B60" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-026-043</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="46" t="inlineStr">
+        <is>
+          <t>Đối tượng tổng hợp được tách theo loại báo biểu (#56597)</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="11" t="n"/>
+      <c r="J60" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (có quyền `report.export_meibo`)
+・Dưới cùng một chi nhánh quản lý・cửa hàng bán có thật, tồn tại người đọc đang đọc báo trong kỳ xuất như sau
+・(a) Bản giấy (dokusya_shubetsu=1) 2 người
+・(b) Kết hợp (3)・trả phí (denshi_dokusya_shubetsu=1) 1 người
+・(c) Kết hợp (3)・miễn phí (denshi_dokusya_shubetsu=0) 1 người
+・(d) Bản điện tử (2)・trả phí・đã duyệt (denshi_shonin_status=1) 1 người
+・(e) Bản điện tử (2)・trả phí・chưa duyệt 1 người
+・(f) Bản điện tử (2)・miễn phí・đã duyệt 1 người
+・Số bản đọc của (b) là 2 bản</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="11" t="n"/>
+      <c r="Q60" s="46" t="inlineStr"/>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="11" t="n"/>
+      <c r="X60" s="46" t="inlineStr"/>
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="11" t="n"/>
+      <c r="AE60" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF60" s="11" t="n"/>
+      <c r="AG60" s="45" t="inlineStr"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="11" t="n"/>
+      <c r="AJ60" s="45" t="inlineStr"/>
+      <c r="AK60" s="10" t="n"/>
+      <c r="AL60" s="11" t="n"/>
+      <c r="AM60" s="45" t="inlineStr"/>
+      <c r="AN60" s="10" t="n"/>
+      <c r="AO60" s="11" t="n"/>
+      <c r="AP60" s="45" t="inlineStr"/>
+      <c r="AQ60" s="10" t="n"/>
+      <c r="AR60" s="11" t="n"/>
+      <c r="AS60" s="45" t="inlineStr"/>
+      <c r="AT60" s="10" t="n"/>
+      <c r="AU60" s="11" t="n"/>
+      <c r="AV60" s="45" t="inlineStr"/>
+      <c r="AW60" s="10" t="n"/>
+      <c r="AX60" s="11" t="n"/>
+      <c r="AY60" s="45" t="inlineStr"/>
+      <c r="AZ60" s="10" t="n"/>
+      <c r="BA60" s="11" t="n"/>
+      <c r="BB60" s="45" t="inlineStr"/>
+      <c r="BC60" s="10" t="n"/>
+      <c r="BD60" s="11" t="n"/>
+      <c r="BE60" s="45" t="inlineStr"/>
+      <c r="BF60" s="10" t="n"/>
+      <c r="BG60" s="11" t="n"/>
+      <c r="BH60" s="45" t="inlineStr"/>
+      <c r="BI60" s="10" t="n"/>
+      <c r="BJ60" s="11" t="n"/>
+      <c r="BK60" s="46" t="inlineStr"/>
+      <c r="BL60" s="10" t="n"/>
+      <c r="BM60" s="10" t="n"/>
+      <c r="BN60" s="10" t="n"/>
+      <c r="BO60" s="10" t="n"/>
+      <c r="BP60" s="10" t="n"/>
+      <c r="BQ60" s="11" t="n"/>
+    </row>
+    <row r="61" ht="144" customHeight="1">
+      <c r="A61" s="44" t="n">
+        <v>44</v>
+      </c>
+      <c r="B61" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-026-044</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="46" t="inlineStr">
+        <is>
+          <t>Cửa hàng bán dummy của bản điện tử bị loại khỏi lựa chọn (#56597)</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (có quyền `report.export_meibo`)
+・JA của mình có cửa hàng bán dummy của bản điện tử (`hanbaiten_code = 9999999999`)
+・Có người đọc bản điện tử gắn với cửa hàng dummy
+・Cũng tồn tại từ 2 cửa hàng bán có thật trở lên</t>
+        </is>
+      </c>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="11" t="n"/>
+      <c r="Q61" s="46" t="inlineStr"/>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="11" t="n"/>
+      <c r="X61" s="46" t="inlineStr"/>
+      <c r="Y61" s="10" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="10" t="n"/>
+      <c r="AD61" s="11" t="n"/>
+      <c r="AE61" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF61" s="11" t="n"/>
+      <c r="AG61" s="45" t="inlineStr"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="11" t="n"/>
+      <c r="AJ61" s="45" t="inlineStr"/>
+      <c r="AK61" s="10" t="n"/>
+      <c r="AL61" s="11" t="n"/>
+      <c r="AM61" s="45" t="inlineStr"/>
+      <c r="AN61" s="10" t="n"/>
+      <c r="AO61" s="11" t="n"/>
+      <c r="AP61" s="45" t="inlineStr"/>
+      <c r="AQ61" s="10" t="n"/>
+      <c r="AR61" s="11" t="n"/>
+      <c r="AS61" s="45" t="inlineStr"/>
+      <c r="AT61" s="10" t="n"/>
+      <c r="AU61" s="11" t="n"/>
+      <c r="AV61" s="45" t="inlineStr"/>
+      <c r="AW61" s="10" t="n"/>
+      <c r="AX61" s="11" t="n"/>
+      <c r="AY61" s="45" t="inlineStr"/>
+      <c r="AZ61" s="10" t="n"/>
+      <c r="BA61" s="11" t="n"/>
+      <c r="BB61" s="45" t="inlineStr"/>
+      <c r="BC61" s="10" t="n"/>
+      <c r="BD61" s="11" t="n"/>
+      <c r="BE61" s="45" t="inlineStr"/>
+      <c r="BF61" s="10" t="n"/>
+      <c r="BG61" s="11" t="n"/>
+      <c r="BH61" s="45" t="inlineStr"/>
+      <c r="BI61" s="10" t="n"/>
+      <c r="BJ61" s="11" t="n"/>
+      <c r="BK61" s="46" t="inlineStr"/>
+      <c r="BL61" s="10" t="n"/>
+      <c r="BM61" s="10" t="n"/>
+      <c r="BN61" s="10" t="n"/>
+      <c r="BO61" s="10" t="n"/>
+      <c r="BP61" s="10" t="n"/>
+      <c r="BQ61" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="768">
+  <mergeCells count="820">
+    <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
+    <mergeCell ref="B60:D60"/>
     <mergeCell ref="Q27:W27"/>
     <mergeCell ref="AS46:AU46"/>
     <mergeCell ref="AE54:AF54"/>
@@ -13861,8 +14277,10 @@
     <mergeCell ref="AE41:AF41"/>
     <mergeCell ref="AV57:AX57"/>
     <mergeCell ref="B53:D53"/>
+    <mergeCell ref="AP60:AR60"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="E14:I14"/>
+    <mergeCell ref="AS61:AU61"/>
     <mergeCell ref="W7:Y7"/>
     <mergeCell ref="AS48:AU48"/>
     <mergeCell ref="BK16:BQ16"/>
@@ -13925,6 +14343,7 @@
     <mergeCell ref="AP28:AR28"/>
     <mergeCell ref="AE57:AF57"/>
     <mergeCell ref="BK53:BQ53"/>
+    <mergeCell ref="BH60:BJ60"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
@@ -13933,14 +14352,17 @@
     <mergeCell ref="BK13:BQ13"/>
     <mergeCell ref="AY57:BA57"/>
     <mergeCell ref="BE41:BG41"/>
+    <mergeCell ref="Q59:W59"/>
     <mergeCell ref="J25:P25"/>
     <mergeCell ref="Q46:W46"/>
     <mergeCell ref="BH55:BJ55"/>
     <mergeCell ref="AM24:AO24"/>
     <mergeCell ref="AG27:AI27"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="AM60:AO60"/>
     <mergeCell ref="BB38:BD38"/>
     <mergeCell ref="AV14:AX14"/>
+    <mergeCell ref="Q61:W61"/>
     <mergeCell ref="W3:AH3"/>
     <mergeCell ref="E33:I33"/>
     <mergeCell ref="Q48:W48"/>
@@ -14005,10 +14427,13 @@
     <mergeCell ref="BE56:BG56"/>
     <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
+    <mergeCell ref="BB59:BD59"/>
     <mergeCell ref="X27:AD27"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="AY60:BA60"/>
+    <mergeCell ref="BB61:BD61"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
     <mergeCell ref="E34:I34"/>
@@ -14042,6 +14467,7 @@
     <mergeCell ref="BE44:BG44"/>
     <mergeCell ref="AP19:AR19"/>
     <mergeCell ref="AJ57:AL57"/>
+    <mergeCell ref="AG61:AI61"/>
     <mergeCell ref="BE31:BG31"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="AG48:AI48"/>
@@ -14086,6 +14512,7 @@
     <mergeCell ref="BB51:BD51"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="AY55:BA55"/>
+    <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
     <mergeCell ref="BK19:BQ19"/>
@@ -14108,6 +14535,7 @@
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="BE53:BG53"/>
+    <mergeCell ref="AJ60:AL60"/>
     <mergeCell ref="AM32:AO32"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="AM26:AO26"/>
@@ -14116,8 +14544,10 @@
     <mergeCell ref="Q20:W20"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="Q14:W14"/>
+    <mergeCell ref="B59:D59"/>
     <mergeCell ref="E57:I57"/>
     <mergeCell ref="B46:D46"/>
+    <mergeCell ref="Q60:W60"/>
     <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
@@ -14141,6 +14571,7 @@
     <mergeCell ref="X51:AD51"/>
     <mergeCell ref="AJ13:AL13"/>
     <mergeCell ref="AM52:AO52"/>
+    <mergeCell ref="BH61:BJ61"/>
     <mergeCell ref="AG17:AI17"/>
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="AM39:AO39"/>
@@ -14153,7 +14584,10 @@
     <mergeCell ref="J52:P52"/>
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="Q25:W25"/>
+    <mergeCell ref="E60:I60"/>
+    <mergeCell ref="AV60:AX60"/>
     <mergeCell ref="Q33:W33"/>
+    <mergeCell ref="X61:AD61"/>
     <mergeCell ref="BK27:BQ27"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="AE29:AF29"/>
@@ -14181,6 +14615,7 @@
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
     <mergeCell ref="A30:BQ30"/>
+    <mergeCell ref="B61:D61"/>
     <mergeCell ref="J47:P47"/>
     <mergeCell ref="BB20:BD20"/>
     <mergeCell ref="BB14:BD14"/>
@@ -14188,13 +14623,17 @@
     <mergeCell ref="AJ28:AL28"/>
     <mergeCell ref="BK17:BQ17"/>
     <mergeCell ref="BK55:BQ55"/>
+    <mergeCell ref="BB60:BD60"/>
+    <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AP46:AR46"/>
+    <mergeCell ref="BK59:BQ59"/>
     <mergeCell ref="BK46:BQ46"/>
     <mergeCell ref="BK40:BQ40"/>
     <mergeCell ref="AE42:AF42"/>
     <mergeCell ref="AS57:AU57"/>
     <mergeCell ref="AY19:BA19"/>
     <mergeCell ref="BK25:BQ25"/>
+    <mergeCell ref="AP61:AR61"/>
     <mergeCell ref="AM16:AO16"/>
     <mergeCell ref="AP48:AR48"/>
     <mergeCell ref="AE44:AF44"/>
@@ -14202,6 +14641,7 @@
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="AP41:AR41"/>
     <mergeCell ref="AM18:AO18"/>
+    <mergeCell ref="J60:P60"/>
     <mergeCell ref="BK41:BQ41"/>
     <mergeCell ref="BB13:BD13"/>
     <mergeCell ref="AM17:AO17"/>
@@ -14240,6 +14680,7 @@
     <mergeCell ref="AJ34:AL34"/>
     <mergeCell ref="Q6:S6"/>
     <mergeCell ref="BK34:BQ34"/>
+    <mergeCell ref="AY59:BA59"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
     <mergeCell ref="AJ49:AL49"/>
@@ -14254,6 +14695,7 @@
     <mergeCell ref="AJ29:AL29"/>
     <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
+    <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
     <mergeCell ref="BE18:BG18"/>
@@ -14264,6 +14706,8 @@
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
+    <mergeCell ref="AE60:AF60"/>
+    <mergeCell ref="AV59:AX59"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="E16:I16"/>
     <mergeCell ref="AV46:AX46"/>
@@ -14273,13 +14717,19 @@
     <mergeCell ref="BK56:BQ56"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="AE45:AF45"/>
+    <mergeCell ref="AS60:AU60"/>
+    <mergeCell ref="AV61:AX61"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AP51:AR51"/>
+    <mergeCell ref="AG59:AI59"/>
     <mergeCell ref="BK51:BQ51"/>
+    <mergeCell ref="X60:AD60"/>
+    <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="BB54:BD54"/>
+    <mergeCell ref="AE59:AF59"/>
     <mergeCell ref="AE22:AF22"/>
     <mergeCell ref="BB41:BD41"/>
     <mergeCell ref="J46:P46"/>
@@ -14290,6 +14740,7 @@
     <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
+    <mergeCell ref="J61:P61"/>
     <mergeCell ref="AY11:BA11"/>
     <mergeCell ref="Q57:W57"/>
     <mergeCell ref="J48:P48"/>
@@ -14354,6 +14805,7 @@
     <mergeCell ref="E19:I19"/>
     <mergeCell ref="BE52:BG52"/>
     <mergeCell ref="BB56:BD56"/>
+    <mergeCell ref="AE61:AF61"/>
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AJ32:AL32"/>
@@ -14362,6 +14814,7 @@
     <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="BB57:BD57"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="AY61:BA61"/>
     <mergeCell ref="AV16:AX16"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="AJ27:AL27"/>
@@ -14373,6 +14826,7 @@
     <mergeCell ref="X33:AD33"/>
     <mergeCell ref="AV17:AX17"/>
     <mergeCell ref="AY56:BA56"/>
+    <mergeCell ref="AM59:AO59"/>
     <mergeCell ref="AV11:AX11"/>
     <mergeCell ref="AP20:AR20"/>
     <mergeCell ref="AY43:BA43"/>
@@ -14385,6 +14839,7 @@
     <mergeCell ref="BH43:BJ43"/>
     <mergeCell ref="BE47:BG47"/>
     <mergeCell ref="AP22:AR22"/>
+    <mergeCell ref="BK60:BQ60"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="J18:P18"/>
     <mergeCell ref="AE18:AF18"/>
@@ -14407,6 +14862,7 @@
     <mergeCell ref="AY34:BA34"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="J19:P19"/>
+    <mergeCell ref="BH59:BJ59"/>
     <mergeCell ref="AY25:BA25"/>
     <mergeCell ref="AS34:AU34"/>
     <mergeCell ref="BB45:BD45"/>
@@ -14418,6 +14874,7 @@
     <mergeCell ref="X34:AD34"/>
     <mergeCell ref="X28:AD28"/>
     <mergeCell ref="BB47:BD47"/>
+    <mergeCell ref="AG60:AI60"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
     <mergeCell ref="BH54:BJ54"/>
@@ -14432,6 +14889,7 @@
     <mergeCell ref="BH31:BJ31"/>
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="AV42:AX42"/>
+    <mergeCell ref="BE59:BG59"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="X54:AD54"/>
     <mergeCell ref="BK20:BQ20"/>
@@ -14461,6 +14919,7 @@
     <mergeCell ref="BH11:BJ11"/>
     <mergeCell ref="AE19:AF19"/>
     <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="AS26:AU26"/>
     <mergeCell ref="AJ46:AL46"/>
@@ -14473,6 +14932,7 @@
     <mergeCell ref="AP23:AR23"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="J20:P20"/>
+    <mergeCell ref="AJ61:AL61"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="BE51:BG51"/>
@@ -14498,6 +14958,7 @@
     <mergeCell ref="BH57:BJ57"/>
     <mergeCell ref="AG13:AI13"/>
     <mergeCell ref="AV33:AX33"/>
+    <mergeCell ref="BE61:BG61"/>
     <mergeCell ref="AP36:AR36"/>
     <mergeCell ref="X39:AD39"/>
     <mergeCell ref="AE14:AF14"/>
@@ -14509,11 +14970,13 @@
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E59:I59"/>
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="J40:P40"/>
     <mergeCell ref="J15:P15"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="E61:I61"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
@@ -14526,6 +14989,7 @@
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
+    <mergeCell ref="A58:BQ58"/>
     <mergeCell ref="F3:Q3"/>
     <mergeCell ref="E56:I56"/>
     <mergeCell ref="AP29:AR29"/>
@@ -14598,6 +15062,7 @@
     <mergeCell ref="B55:D55"/>
     <mergeCell ref="AM25:AO25"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
     <mergeCell ref="BE19:BG19"/>
@@ -14620,15 +15085,16 @@
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="AV56:AX56"/>
+    <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE20 AE22:AE29 AE31:AE36 AE38:AE49 AE51:AE57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE20 AE22:AE29 AE31:AE36 AE38:AE49 AE51:AE57 AE59:AE61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG20 AG22:AG29 AG31:AG36 AG38:AG49 AG51:AG57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG20 AG22:AG29 AG31:AG36 AG38:AG49 AG51:AG57 AG59:AG61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV20 AV22:AV29 AV31:AV36 AV38:AV49 AV51:AV57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV20 AV22:AV29 AV31:AV36 AV38:AV49 AV51:AV57 AV59:AV61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
